--- a/HardwareSemis.xlsx
+++ b/HardwareSemis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D94FD3-78A0-4BE5-A0C9-E76710B22B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341140F6-4B7D-4A25-9110-5D6D7D691DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42210" yWindow="2550" windowWidth="23430" windowHeight="16240" xr2:uid="{98D8347A-DFA4-427C-8784-96E5573B433C}"/>
+    <workbookView xWindow="17280" yWindow="2750" windowWidth="19980" windowHeight="16070" xr2:uid="{98D8347A-DFA4-427C-8784-96E5573B433C}"/>
   </bookViews>
   <sheets>
     <sheet name="Semiconductors" sheetId="1" r:id="rId1"/>
@@ -42,6 +42,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="CNY">FX!$B$4</definedName>
+    <definedName name="JPY">FX!$C$6</definedName>
     <definedName name="KRW">FX!$C$3</definedName>
     <definedName name="None">FX!$B$4</definedName>
   </definedNames>
@@ -87,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="264">
   <si>
     <t>Name</t>
   </si>
@@ -852,6 +853,33 @@
   </si>
   <si>
     <t>P/E</t>
+  </si>
+  <si>
+    <t>Silicon Spin Qubits</t>
+  </si>
+  <si>
+    <t>3661 TT</t>
+  </si>
+  <si>
+    <t>AIchip</t>
+  </si>
+  <si>
+    <t>Global Unichip</t>
+  </si>
+  <si>
+    <t>3443 TT</t>
+  </si>
+  <si>
+    <t>Faraday</t>
+  </si>
+  <si>
+    <t>3035 TT</t>
+  </si>
+  <si>
+    <t>TWD</t>
+  </si>
+  <si>
+    <t>JPY</t>
   </si>
 </sst>
 </file>
@@ -862,7 +890,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="[$₩-412]#,##0"/>
     <numFmt numFmtId="166" formatCode="[$¥-804]#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0\x"/>
+    <numFmt numFmtId="167" formatCode="0\x"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -948,10 +976,10 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -988,17 +1016,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="K3">
-            <v>24611</v>
+            <v>24300</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>53691</v>
+            <v>56791</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>8464</v>
+            <v>8466</v>
           </cell>
         </row>
       </sheetData>
@@ -1163,7 +1191,7 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>296.83779600000003</v>
+            <v>354.27959099999998</v>
           </cell>
         </row>
         <row r="5">
@@ -1243,17 +1271,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>286</v>
+            <v>346.71858099999997</v>
           </cell>
         </row>
         <row r="5">
           <cell r="L5">
-            <v>304.32100000000003</v>
+            <v>836.23099999999999</v>
           </cell>
         </row>
         <row r="6">
           <cell r="L6">
-            <v>30.367000000000001</v>
+            <v>32.198</v>
           </cell>
         </row>
       </sheetData>
@@ -1279,34 +1307,34 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="O3">
-            <v>15056</v>
+            <v>14948</v>
           </cell>
         </row>
         <row r="5">
           <cell r="O5">
-            <v>132922</v>
+            <v>132986</v>
           </cell>
         </row>
         <row r="6">
           <cell r="O6">
-            <v>98186</v>
+            <v>101698</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="36">
           <cell r="CE36">
-            <v>7.4999999999999997E-2</v>
+            <v>4.1953407917453944E-2</v>
           </cell>
         </row>
         <row r="37">
           <cell r="CE37">
-            <v>-0.01</v>
+            <v>3.632000000000013E-2</v>
           </cell>
         </row>
         <row r="39">
           <cell r="CE39">
-            <v>158.7822866043505</v>
+            <v>0.46906012207980208</v>
           </cell>
         </row>
       </sheetData>
@@ -1398,17 +1426,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>4836</v>
+            <v>4860</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>9307</v>
+            <v>10718</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>66579</v>
+            <v>64229</v>
           </cell>
         </row>
       </sheetData>
@@ -1437,12 +1465,12 @@
         </row>
         <row r="7">
           <cell r="J7">
-            <v>67370</v>
+            <v>94986</v>
           </cell>
         </row>
         <row r="8">
           <cell r="J8">
-            <v>30421</v>
+            <v>2900034</v>
           </cell>
         </row>
       </sheetData>
@@ -1500,21 +1528,21 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="M3">
-            <v>1630</v>
+            <v>1641</v>
           </cell>
         </row>
         <row r="5">
           <cell r="M5">
-            <v>5867</v>
+            <v>7243</v>
           </cell>
         </row>
         <row r="6">
           <cell r="M6">
-            <v>3218</v>
+            <v>3220</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1605,17 +1633,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>4267</v>
+            <v>4531</v>
           </cell>
         </row>
         <row r="5">
           <cell r="L5">
-            <v>35097</v>
+            <v>39602</v>
           </cell>
         </row>
         <row r="6">
           <cell r="L6">
-            <v>53029</v>
+            <v>46553</v>
           </cell>
         </row>
       </sheetData>
@@ -1959,35 +1987,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B77F9E42-3F4A-4F5B-8F7C-4C05A85AC67E}">
-  <dimension ref="A1:U51"/>
+  <dimension ref="A1:U54"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.453125" customWidth="1"/>
     <col min="2" max="2" width="17.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="9.1796875" style="3"/>
-    <col min="5" max="5" width="9.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="3"/>
-    <col min="7" max="7" width="9.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.54296875" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9.1796875" style="3"/>
     <col min="10" max="10" width="11.81640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17" t="s">
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
@@ -2072,19 +2098,19 @@
       </c>
       <c r="E3" s="6">
         <f>+D3*H3</f>
-        <v>4774534</v>
+        <v>4714200</v>
       </c>
       <c r="F3" s="6">
         <f>+[1]Main!$K$5-[1]Main!$K$6</f>
-        <v>45227</v>
+        <v>48325</v>
       </c>
       <c r="G3" s="6">
         <f>+E3-F3</f>
-        <v>4729307</v>
+        <v>4665875</v>
       </c>
       <c r="H3" s="6">
         <f>+[1]Main!$K$3</f>
-        <v>24611</v>
+        <v>24300</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>196</v>
@@ -2111,19 +2137,19 @@
       </c>
       <c r="E4" s="6">
         <f>+D4*H4</f>
-        <v>1663584</v>
+        <v>1671840</v>
       </c>
       <c r="F4" s="6">
         <f>+[2]Main!$J$5-[2]Main!$J$6</f>
-        <v>-57272</v>
+        <v>-53511</v>
       </c>
       <c r="G4" s="6">
         <f>+E4-F4</f>
-        <v>1720856</v>
+        <v>1725351</v>
       </c>
       <c r="H4" s="6">
         <f>+[2]Main!$J$3</f>
-        <v>4836</v>
+        <v>4860</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>120</v>
@@ -2150,12 +2176,12 @@
         <v>1557363.9980000001</v>
       </c>
       <c r="F5" s="6">
-        <f>+[3]Main!$J$7-[3]Main!$J$8</f>
-        <v>36949</v>
+        <f>([3]Main!$J$7-[3]Main!$J$8)/FX!C5</f>
+        <v>-87849.921703726897</v>
       </c>
       <c r="G5" s="6">
         <f>+E5-F5</f>
-        <v>1520414.9980000001</v>
+        <v>1645213.9197037271</v>
       </c>
       <c r="H5" s="6">
         <f>+[3]Main!$J$4</f>
@@ -2186,12 +2212,12 @@
         <v>1142614.4430844553</v>
       </c>
       <c r="F6" s="6">
-        <f>+[3]Main!$J$7-[3]Main!$J$8</f>
-        <v>36949</v>
+        <f>([3]Main!$J$7-[3]Main!$J$8)/FX!C5</f>
+        <v>-87849.921703726897</v>
       </c>
       <c r="G6" s="6">
         <f>+E6-F6</f>
-        <v>1105665.4430844553</v>
+        <v>1230464.3647881823</v>
       </c>
       <c r="H6" s="6">
         <f>+[3]Main!$J$4</f>
@@ -2217,7 +2243,11 @@
         <v>23</v>
       </c>
       <c r="D7" s="6">
-        <v>89000</v>
+        <v>191600</v>
+      </c>
+      <c r="E7" s="6">
+        <f>1270340000/KRW</f>
+        <v>875040.46840020665</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -2231,11 +2261,11 @@
         <v>25</v>
       </c>
       <c r="D8" s="4">
-        <v>983</v>
+        <v>1348</v>
       </c>
       <c r="E8" s="6">
         <f>+D8*H8</f>
-        <v>386810.5</v>
+        <v>530438</v>
       </c>
       <c r="F8" s="6">
         <f>+[4]Main!$L$5-[4]Main!$L$6</f>
@@ -2243,7 +2273,7 @@
       </c>
       <c r="G8" s="6">
         <f>+E8-F8</f>
-        <v>385397.5</v>
+        <v>529025</v>
       </c>
       <c r="H8" s="6">
         <f>+[4]Main!$L$3</f>
@@ -2260,378 +2290,460 @@
       <c r="A9" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
+      <c r="B9" t="s">
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="4">
-        <v>238</v>
+        <v>54</v>
+      </c>
+      <c r="D9" s="6">
+        <v>941000</v>
       </c>
       <c r="E9" s="6">
-        <f>+D9*H9</f>
-        <v>387940</v>
-      </c>
-      <c r="F9" s="6">
-        <f>+[5]Main!$M$5-[5]Main!$M$6</f>
-        <v>2649</v>
-      </c>
-      <c r="G9" s="6">
-        <f>+E9-F9</f>
-        <v>385291</v>
-      </c>
-      <c r="H9" s="6">
-        <f>+[5]Main!$M$3</f>
-        <v>1630</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J9" s="10">
-        <v>45939</v>
-      </c>
-      <c r="K9">
-        <v>1969</v>
-      </c>
-      <c r="L9">
-        <v>3.84</v>
-      </c>
-      <c r="M9">
-        <v>6.14</v>
-      </c>
-      <c r="Q9" s="18">
-        <f>+$D9/L9</f>
-        <v>61.979166666666671</v>
-      </c>
-      <c r="R9" s="18">
-        <f>+$D9/M9</f>
-        <v>38.762214983713356</v>
-      </c>
-      <c r="S9" s="18"/>
-      <c r="T9" s="18"/>
+        <f>649720/KRW*1000</f>
+        <v>447542.62097468576</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D10" s="3">
-        <v>171.54</v>
+        <v>383</v>
       </c>
       <c r="E10" s="6">
         <f>+D10*H10</f>
+        <v>424686.22785799997</v>
+      </c>
+      <c r="F10" s="6">
+        <f>+[9]Main!$J$5-[9]Main!$J$6</f>
+        <v>-4104</v>
+      </c>
+      <c r="G10" s="6">
+        <f>+E10-F10</f>
+        <v>428790.22785799997</v>
+      </c>
+      <c r="H10" s="6">
+        <f>+[9]Main!$J$3</f>
+        <v>1108.841326</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J10" s="10">
+        <v>45554</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="4">
+        <v>196.25</v>
+      </c>
+      <c r="E11" s="6">
+        <f>+D11*H11</f>
+        <v>322046.25</v>
+      </c>
+      <c r="F11" s="6">
+        <f>+[5]Main!$M$5-[5]Main!$M$6</f>
+        <v>4023</v>
+      </c>
+      <c r="G11" s="6">
+        <f>+E11-F11</f>
+        <v>318023.25</v>
+      </c>
+      <c r="H11" s="6">
+        <f>+[5]Main!$M$3</f>
+        <v>1641</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="J11" s="10">
+        <v>45939</v>
+      </c>
+      <c r="K11">
+        <v>1969</v>
+      </c>
+      <c r="L11">
+        <v>3.84</v>
+      </c>
+      <c r="M11">
+        <v>6.14</v>
+      </c>
+      <c r="Q11" s="17">
+        <f>+$D11/L11</f>
+        <v>51.106770833333336</v>
+      </c>
+      <c r="R11" s="17">
+        <f>+$D11/M11</f>
+        <v>31.962540716612381</v>
+      </c>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3">
+        <v>337.09</v>
+      </c>
+      <c r="E12" s="6">
+        <v>267520</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="3">
+        <v>208.87</v>
+      </c>
+      <c r="E13" s="6">
+        <v>260830</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4">
+        <v>45.22</v>
+      </c>
+      <c r="E14" s="6">
+        <f>+D14*H14</f>
+        <v>204891.82</v>
+      </c>
+      <c r="F14" s="6">
+        <f>+[8]Main!$L$5-[8]Main!$L$6</f>
+        <v>-6951</v>
+      </c>
+      <c r="G14" s="6">
+        <f>+E14-F14</f>
+        <v>211842.82</v>
+      </c>
+      <c r="H14" s="6">
+        <f>+[8]Main!$L$3</f>
+        <v>4531</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="10">
+        <v>45507</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="3">
+        <v>171.54</v>
+      </c>
+      <c r="E15" s="6">
+        <f>+D15*H15</f>
         <v>191095.56</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F15" s="6">
         <f>+[6]Main!$L$5-[6]Main!$L$6</f>
         <v>-1522</v>
       </c>
-      <c r="G10" s="6">
-        <f>+E10-F10</f>
+      <c r="G15" s="6">
+        <f>+E15-F15</f>
         <v>192617.56</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H15" s="6">
         <f>+[6]Main!$L$3</f>
         <v>1114</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J15" s="10">
         <v>45581</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="1" t="s">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1393</v>
+      </c>
+      <c r="E16" s="6">
+        <v>182590</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="3">
+        <v>327.88</v>
+      </c>
+      <c r="E17" s="6">
+        <v>160070</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="3">
-        <v>170.34</v>
-      </c>
-      <c r="E11" s="6">
-        <f>+D11*H11</f>
-        <v>154595.76542208</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="D18" s="3">
+        <v>196.78</v>
+      </c>
+      <c r="E18" s="6">
+        <f>+D18*H18</f>
+        <v>178591.96148736001</v>
+      </c>
+      <c r="F18" s="6">
         <f>+[7]Main!$K$5-[7]Main!$K$6</f>
         <v>1153</v>
       </c>
-      <c r="G11" s="6">
-        <f>+E11-F11</f>
-        <v>153442.76542208</v>
-      </c>
-      <c r="H11" s="6">
+      <c r="G18" s="6">
+        <f>+E18-F18</f>
+        <v>177438.96148736001</v>
+      </c>
+      <c r="H18" s="6">
         <f>+[7]Main!$K$3</f>
         <v>907.57171200000005</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J18" s="10">
         <v>44946</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="4">
-        <v>19.91</v>
-      </c>
-      <c r="E12" s="6">
-        <f>+D12*H12</f>
-        <v>84955.97</v>
-      </c>
-      <c r="F12" s="6">
-        <f>+[8]Main!$L$5-[8]Main!$L$6</f>
-        <v>-17932</v>
-      </c>
-      <c r="G12" s="6">
-        <f>+E12-F12</f>
-        <v>102887.97</v>
-      </c>
-      <c r="H12" s="6">
-        <f>+[8]Main!$L$3</f>
-        <v>4267</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J12" s="10">
-        <v>45507</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s">
         <v>118</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C19" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="D19" s="3">
+        <v>119.15</v>
+      </c>
+      <c r="E19" s="6">
+        <v>126470</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="6">
+        <v>41720</v>
+      </c>
+      <c r="E20" s="6">
+        <f>124700</f>
+        <v>124700</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>199</v>
+      </c>
+      <c r="C21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D21" s="6">
+        <v>25535</v>
+      </c>
+      <c r="E21" s="6">
+        <v>119990</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1775</v>
+      </c>
+      <c r="E22" s="6">
+        <f>2830000/FX!$C$2</f>
+        <v>86597.307221542229</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="6">
+        <v>6226</v>
+      </c>
+      <c r="E23" s="6">
+        <v>73070</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="4">
+        <v>209.6</v>
+      </c>
+      <c r="E24" s="6">
+        <v>52970</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="3">
+        <v>67.91</v>
+      </c>
+      <c r="E25" s="6">
+        <v>36740</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C26" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="3">
-        <v>89.54</v>
-      </c>
-      <c r="E17" s="6">
-        <f>+D17*H17</f>
-        <v>99285.65233004</v>
-      </c>
-      <c r="F17" s="6">
-        <f>+[9]Main!$J$5-[9]Main!$J$6</f>
-        <v>-4104</v>
-      </c>
-      <c r="G17" s="6">
-        <f>+E17-F17</f>
-        <v>103389.65233004</v>
-      </c>
-      <c r="H17" s="6">
-        <f>+[9]Main!$J$3</f>
-        <v>1108.841326</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J17" s="10">
-        <v>45554</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="D26" s="3">
+        <v>17.760000000000002</v>
+      </c>
+      <c r="E26" s="6">
+        <f>134230/CNY</f>
+        <v>19175.714285714286</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C27" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D27" s="4">
         <v>20.65</v>
       </c>
-      <c r="E18" s="6">
-        <f>+D18*H18</f>
+      <c r="E27" s="6">
+        <f>+D27*H27</f>
         <v>13216</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F27" s="6">
         <f>+[10]Main!$M$5-[10]Main!$M$6</f>
         <v>-504</v>
       </c>
-      <c r="G18" s="6">
-        <f>+E18-F18</f>
+      <c r="G27" s="6">
+        <f>+E27-F27</f>
         <v>13720</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H27" s="6">
         <f>+[10]Main!$M$3</f>
         <v>640</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J27" s="10">
         <v>45560</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" t="s">
-        <v>199</v>
-      </c>
-      <c r="C26" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" t="s">
-        <v>201</v>
-      </c>
-      <c r="C27" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2639,10 +2751,10 @@
         <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C28" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2650,10 +2762,10 @@
         <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2699,6 +2811,12 @@
       <c r="C33" t="s">
         <v>94</v>
       </c>
+      <c r="D33" s="3">
+        <v>32.51</v>
+      </c>
+      <c r="E33" s="6">
+        <v>28890</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
@@ -2743,6 +2861,12 @@
       <c r="C37" t="s">
         <v>224</v>
       </c>
+      <c r="D37" s="4">
+        <v>717</v>
+      </c>
+      <c r="E37" s="6">
+        <v>41130</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
@@ -2754,49 +2878,67 @@
       <c r="C38" t="s">
         <v>240</v>
       </c>
+      <c r="D38" s="4">
+        <v>353.5</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
-        <v>46</v>
-      </c>
+      <c r="A39" s="14"/>
       <c r="B39" t="s">
+        <v>257</v>
+      </c>
+      <c r="C39" t="s">
+        <v>256</v>
+      </c>
+      <c r="D39" s="4">
+        <v>3270</v>
+      </c>
+      <c r="E39" s="6">
+        <f>264920/FX!$C$5</f>
+        <v>8296.8994675853428</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" t="s">
         <v>241</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" t="s">
-        <v>99</v>
-      </c>
-      <c r="C40" t="s">
-        <v>100</v>
-      </c>
-    </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>46</v>
-      </c>
+      <c r="A41" s="14"/>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>258</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>259</v>
+      </c>
+      <c r="D41" s="4">
+        <v>2355</v>
+      </c>
+      <c r="E41" s="6">
+        <f>315600/FX!$C$5</f>
+        <v>9884.1215158158466</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>46</v>
-      </c>
+      <c r="A42" s="14"/>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>260</v>
       </c>
       <c r="C42" t="s">
-        <v>110</v>
+        <v>261</v>
+      </c>
+      <c r="D42" s="4">
+        <v>159</v>
+      </c>
+      <c r="E42" s="6">
+        <f>41430/FX!$C$5</f>
+        <v>1297.5258377701221</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2804,10 +2946,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>248</v>
+        <v>99</v>
       </c>
       <c r="C43" t="s">
-        <v>249</v>
+        <v>100</v>
+      </c>
+      <c r="D43" s="4">
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2815,123 +2960,174 @@
         <v>46</v>
       </c>
       <c r="B44" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="3">
+        <v>47.15</v>
+      </c>
+      <c r="E44" s="6">
+        <v>26330</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" s="3">
+        <v>60.46</v>
+      </c>
+      <c r="E45" s="6">
+        <v>23800</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>248</v>
+      </c>
+      <c r="C46" t="s">
+        <v>249</v>
+      </c>
+      <c r="D46" s="3">
+        <v>118.63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
         <v>111</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C47" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="1" t="s">
+      <c r="D47" s="4">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C48" t="s">
         <v>135</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D48" s="4">
         <v>112</v>
       </c>
-      <c r="E45" s="6">
-        <f>+D45*H45</f>
+      <c r="E48" s="6">
+        <f>+D48*H48</f>
         <v>15167.281808</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F48" s="6">
         <f>+[11]Main!$J$5-[11]Main!$J$6</f>
         <v>446.97199999999998</v>
       </c>
-      <c r="G45" s="6">
-        <f>+E45-F45</f>
+      <c r="G48" s="6">
+        <f>+E48-F48</f>
         <v>14720.309808</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H48" s="6">
         <f>+[11]Main!$J$3</f>
         <v>135.42215899999999</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I48" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J45" s="10">
+      <c r="J48" s="10">
         <v>45561</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C49" t="s">
         <v>137</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D49" s="4">
         <v>13</v>
       </c>
-      <c r="E46" s="6">
-        <f>+D46*H46</f>
+      <c r="E49" s="6">
+        <f>+D49*H49</f>
         <v>10543.625651</v>
       </c>
-      <c r="F46" s="6">
+      <c r="F49" s="6">
         <f>+[12]Main!$K$5-[12]Main!$K$6</f>
         <v>1203</v>
       </c>
-      <c r="G46" s="6">
-        <f>+E46-F46</f>
+      <c r="G49" s="6">
+        <f>+E49-F49</f>
         <v>9340.6256510000003</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H49" s="6">
         <f>+[12]Main!$K$3</f>
         <v>811.04812700000002</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="I49" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J46" s="10">
+      <c r="J49" s="10">
         <v>45561</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="1" t="s">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C50" t="s">
         <v>244</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D50" s="4">
         <v>23.19</v>
       </c>
-      <c r="E47" s="6">
-        <f>+D47*H47</f>
+      <c r="E50" s="6">
+        <f>+D50*H50</f>
         <v>1481.01784776</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F50" s="6">
         <f>+[13]Main!$J$5-[13]Main!$J$6</f>
         <v>295.214</v>
       </c>
-      <c r="G47" s="6">
-        <f>+E47-F47</f>
+      <c r="G50" s="6">
+        <f>+E50-F50</f>
         <v>1185.8038477600001</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H50" s="6">
         <f>+[13]Main!$J$3</f>
         <v>63.864503999999997</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="I50" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="J47" s="10">
+      <c r="J50" s="10">
         <v>45796</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2942,19 +3138,19 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{82B60337-F6F7-4A89-BE21-94E4E4FAE923}"/>
-    <hyperlink ref="B11" r:id="rId2" xr:uid="{89BFBE39-15FE-4D88-BD35-419556A195F8}"/>
-    <hyperlink ref="B12" r:id="rId3" xr:uid="{ACBF0F19-D83E-41D4-B3AD-01439A0CCE2D}"/>
-    <hyperlink ref="B9" r:id="rId4" xr:uid="{0B4AADBB-7802-4155-9477-7B8867856D77}"/>
+    <hyperlink ref="B18" r:id="rId2" xr:uid="{89BFBE39-15FE-4D88-BD35-419556A195F8}"/>
+    <hyperlink ref="B14" r:id="rId3" xr:uid="{ACBF0F19-D83E-41D4-B3AD-01439A0CCE2D}"/>
+    <hyperlink ref="B11" r:id="rId4" xr:uid="{0B4AADBB-7802-4155-9477-7B8867856D77}"/>
     <hyperlink ref="B5" r:id="rId5" xr:uid="{D5C26AF1-ADC4-4E03-9D8B-12F3C24C324B}"/>
     <hyperlink ref="B6" r:id="rId6" xr:uid="{DD4F0CC9-D485-4053-9B41-DE6F39511946}"/>
     <hyperlink ref="B4" r:id="rId7" xr:uid="{05815C98-BE17-4CF3-942D-C5BFAB80DA80}"/>
-    <hyperlink ref="B17" r:id="rId8" xr:uid="{37FE970B-81E9-4AF7-98E1-474982CC16D7}"/>
-    <hyperlink ref="B18" r:id="rId9" xr:uid="{CF0C3BE9-553F-4E6A-8F72-3B6D86F868FC}"/>
-    <hyperlink ref="B45" r:id="rId10" xr:uid="{35D78F35-BD1B-401F-9830-193EF147D21A}"/>
-    <hyperlink ref="B46" r:id="rId11" xr:uid="{8FC74BE2-2095-4EFE-8F49-C1E00A6EF2C6}"/>
-    <hyperlink ref="B10" r:id="rId12" xr:uid="{E7CBB7C3-B2DF-42D5-A84A-8A1B7E26DDB6}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{37FE970B-81E9-4AF7-98E1-474982CC16D7}"/>
+    <hyperlink ref="B27" r:id="rId9" xr:uid="{CF0C3BE9-553F-4E6A-8F72-3B6D86F868FC}"/>
+    <hyperlink ref="B48" r:id="rId10" xr:uid="{35D78F35-BD1B-401F-9830-193EF147D21A}"/>
+    <hyperlink ref="B49" r:id="rId11" xr:uid="{8FC74BE2-2095-4EFE-8F49-C1E00A6EF2C6}"/>
+    <hyperlink ref="B15" r:id="rId12" xr:uid="{E7CBB7C3-B2DF-42D5-A84A-8A1B7E26DDB6}"/>
     <hyperlink ref="B8" r:id="rId13" xr:uid="{3EEE25FB-8581-4AA9-ADEF-37DC0B2F3F4D}"/>
-    <hyperlink ref="B47" r:id="rId14" xr:uid="{3A48277A-E40F-4BB9-B4C3-9290548C0B09}"/>
+    <hyperlink ref="B50" r:id="rId14" xr:uid="{3A48277A-E40F-4BB9-B4C3-9290548C0B09}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2962,7 +3158,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7969B36B-DEE6-4982-80A3-7EB4D6794539}">
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -3025,388 +3221,406 @@
       <c r="K3" s="3"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="6">
+        <v>16000</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>123</v>
       </c>
-      <c r="D4" s="2">
-        <v>51</v>
-      </c>
-      <c r="E4" s="13">
-        <f>+D4*H4</f>
-        <v>15138.727596000001</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="D5" s="2">
+        <v>32</v>
+      </c>
+      <c r="E5" s="13">
+        <f>+D5*H5</f>
+        <v>11336.946911999999</v>
+      </c>
+      <c r="F5" s="13">
         <f>+[14]Main!$J$5-[14]Main!$J$6</f>
         <v>1657</v>
       </c>
-      <c r="G4" s="13">
-        <f>+E4-F4</f>
-        <v>13481.727596000001</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="G5" s="13">
+        <f>+E5-F5</f>
+        <v>9679.9469119999994</v>
+      </c>
+      <c r="H5" s="13">
         <f>+[14]Main!$J$3</f>
-        <v>296.83779600000003</v>
-      </c>
-      <c r="I4" s="3" t="s">
+        <v>354.27959099999998</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J5" s="5">
         <v>45664</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>126</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>7.95</v>
       </c>
-      <c r="E5" s="13">
-        <f>+D5*H5</f>
+      <c r="E6" s="13">
+        <f>+D6*H6</f>
         <v>2254.1976244500001</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F6" s="13">
         <f>+[15]Main!$L$5-[15]Main!$L$6</f>
         <v>217</v>
       </c>
-      <c r="G5" s="13">
-        <f>E5-F5</f>
+      <c r="G6" s="13">
+        <f>E6-F6</f>
         <v>2037.1976244500001</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H6" s="13">
         <f>+[15]Main!$L$3</f>
         <v>283.54687100000001</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J6" s="5">
         <v>45664</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D6" s="2">
-        <v>18</v>
-      </c>
-      <c r="E6" s="13">
-        <v>2000</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" s="2">
+        <v>18</v>
+      </c>
+      <c r="E7" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D8" s="2">
         <v>6.45</v>
       </c>
-      <c r="E7" s="13">
-        <f>+D7*H7</f>
-        <v>1844.7</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="E8" s="13">
+        <f>+D8*H8</f>
+        <v>2236.3348474499999</v>
+      </c>
+      <c r="F8" s="13">
         <f>+[16]Main!$L$5-[16]Main!$L$6</f>
-        <v>273.95400000000001</v>
-      </c>
-      <c r="G7" s="13">
-        <f>+E7-F7</f>
-        <v>1570.7460000000001</v>
-      </c>
-      <c r="H7" s="13">
+        <v>804.03300000000002</v>
+      </c>
+      <c r="G8" s="13">
+        <f>+E8-F8</f>
+        <v>1432.30184745</v>
+      </c>
+      <c r="H8" s="13">
         <f>+[16]Main!$L$3</f>
-        <v>286</v>
-      </c>
-      <c r="I7" s="3" t="s">
+        <v>346.71858099999997</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J8" s="5">
         <v>45663</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>194</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>195</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D9" s="2">
         <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>164</v>
-      </c>
-      <c r="C34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>166</v>
+        <v>164</v>
+      </c>
+      <c r="C35" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
         <v>191</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{48212D98-F0E3-4509-96A5-6BB9683E0B25}"/>
-    <hyperlink ref="B5" r:id="rId2" xr:uid="{F1FD0F3E-AA09-4EA5-ABFA-C8FDF989BBD7}"/>
-    <hyperlink ref="B6" r:id="rId3" xr:uid="{31AE1ADD-F109-4DDC-933D-81406D33D7B1}"/>
-    <hyperlink ref="B7" r:id="rId4" xr:uid="{222626AB-8AD1-4B96-B080-994B3561591D}"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{48212D98-F0E3-4509-96A5-6BB9683E0B25}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{F1FD0F3E-AA09-4EA5-ABFA-C8FDF989BBD7}"/>
+    <hyperlink ref="B7" r:id="rId3" xr:uid="{31AE1ADD-F109-4DDC-933D-81406D33D7B1}"/>
+    <hyperlink ref="B8" r:id="rId4" xr:uid="{222626AB-8AD1-4B96-B080-994B3561591D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3639,19 +3853,19 @@
       </c>
       <c r="E3" s="6">
         <f>+D3*H3</f>
-        <v>3094158.56</v>
+        <v>3071963.48</v>
       </c>
       <c r="F3" s="6">
         <f>+[17]Main!$O$5-[17]Main!$O$6</f>
-        <v>34736</v>
+        <v>31288</v>
       </c>
       <c r="G3" s="6">
         <f>+E3-F3</f>
-        <v>3059422.56</v>
+        <v>3040675.48</v>
       </c>
       <c r="H3" s="6">
         <f>+[17]Main!$O$3</f>
-        <v>15056</v>
+        <v>14948</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>196</v>
@@ -3661,19 +3875,19 @@
       </c>
       <c r="K3" s="2">
         <f>[17]Model!$CE$39</f>
-        <v>158.7822866043505</v>
+        <v>0.46906012207980208</v>
       </c>
       <c r="L3" s="7">
         <f>+K3/D3-1</f>
-        <v>-0.22737440219770078</v>
+        <v>-0.99771758005897615</v>
       </c>
       <c r="M3" s="8">
         <f>+[17]Model!$CE$36</f>
-        <v>7.4999999999999997E-2</v>
+        <v>4.1953407917453944E-2</v>
       </c>
       <c r="N3" s="8">
         <f>+[17]Model!$CE$37</f>
-        <v>-0.01</v>
+        <v>3.632000000000013E-2</v>
       </c>
       <c r="O3" s="8">
         <v>0</v>
@@ -4002,7 +4216,7 @@
       </c>
       <c r="E29" s="6">
         <f>+D29*H29</f>
-        <v>11576.674044000001</v>
+        <v>13816.904048999999</v>
       </c>
       <c r="F29" s="6">
         <f>+[14]Main!$J$5-[14]Main!$J$6</f>
@@ -4010,11 +4224,11 @@
       </c>
       <c r="G29" s="6">
         <f>+E29-F29</f>
-        <v>9919.6740440000012</v>
+        <v>12159.904048999999</v>
       </c>
       <c r="H29" s="6">
         <f>+[14]Main!$J$3</f>
-        <v>296.83779600000003</v>
+        <v>354.27959099999998</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>128</v>
@@ -4160,7 +4374,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC72FDEE-60E0-4B9B-AACF-AB184FD947A1}">
-  <dimension ref="B2:C4"/>
+  <dimension ref="B2:C6"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.1796875" customWidth="1"/>
@@ -4190,6 +4404,22 @@
         <v>218</v>
       </c>
     </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5">
+        <v>31.93</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6">
+        <v>157.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
